--- a/out/thesis/tables/summary_statistics.xlsx
+++ b/out/thesis/tables/summary_statistics.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>metric</t>
   </si>
@@ -61,6 +61,9 @@
     <t>CAR_ANN_NEXT_DAY</t>
   </si>
   <si>
+    <t>ratio_1h_vs_day</t>
+  </si>
+  <si>
     <t>CAR_ANN_1_1</t>
   </si>
   <si>
@@ -76,12 +79,6 @@
     <t>BHAR_ANN_60</t>
   </si>
   <si>
-    <t>BHAR_ANN_120</t>
-  </si>
-  <si>
-    <t>BHAR_ANN_250</t>
-  </si>
-  <si>
     <t>CAR_CLOSE_1_1</t>
   </si>
   <si>
@@ -98,9 +95,6 @@
   </si>
   <si>
     <t>BHAR_CLOSE_120</t>
-  </si>
-  <si>
-    <t>BHAR_CLOSE_250</t>
   </si>
   <si>
     <t>RUNUP_PRE_30_5</t>
@@ -450,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -484,19 +478,19 @@
         <v>61</v>
       </c>
       <c r="C2">
-        <v>0.002091472032654441</v>
+        <v>0.001199727994858157</v>
       </c>
       <c r="D2">
-        <v>0.0009668111176824559</v>
+        <v>0.0001032200883013812</v>
       </c>
       <c r="E2">
-        <v>0.01067804198686488</v>
+        <v>0.006146008555622823</v>
       </c>
       <c r="F2">
-        <v>-0.01583558117167476</v>
+        <v>-0.01057432171809979</v>
       </c>
       <c r="G2">
-        <v>0.06301091157066496</v>
+        <v>0.0362517880771814</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -507,19 +501,19 @@
         <v>61</v>
       </c>
       <c r="C3">
-        <v>0.0007960819640465093</v>
+        <v>-9.566207374977578E-05</v>
       </c>
       <c r="D3">
-        <v>0.0008540995544017836</v>
+        <v>0.0002336781725555482</v>
       </c>
       <c r="E3">
-        <v>0.009848818474812055</v>
+        <v>0.007379119416778246</v>
       </c>
       <c r="F3">
-        <v>-0.02371824587607082</v>
+        <v>-0.02451359356489838</v>
       </c>
       <c r="G3">
-        <v>0.03896874669512307</v>
+        <v>0.02739300227640433</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -576,19 +570,19 @@
         <v>61</v>
       </c>
       <c r="C6">
-        <v>0.00483168657668591</v>
+        <v>0.004379907928898975</v>
       </c>
       <c r="D6">
-        <v>0.005042472615222377</v>
+        <v>0.004567992705071912</v>
       </c>
       <c r="E6">
-        <v>0.04564585736836577</v>
+        <v>0.04492360948754695</v>
       </c>
       <c r="F6">
-        <v>-0.08396301286541893</v>
+        <v>-0.1070767147920283</v>
       </c>
       <c r="G6">
-        <v>0.1493029728468701</v>
+        <v>0.1511130395694213</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -665,22 +659,22 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="C10">
-        <v>0.0004031446113741195</v>
+        <v>17.96630035866757</v>
       </c>
       <c r="D10">
-        <v>0.001734709694305225</v>
+        <v>8.819130144622921</v>
       </c>
       <c r="E10">
-        <v>0.03615776985502361</v>
+        <v>121.7119859414391</v>
       </c>
       <c r="F10">
-        <v>-0.104449111287138</v>
+        <v>-144.4830120544106</v>
       </c>
       <c r="G10">
-        <v>0.1015225232062136</v>
+        <v>622.0153206002653</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -691,19 +685,19 @@
         <v>125</v>
       </c>
       <c r="C11">
-        <v>-0.001243392319941792</v>
+        <v>0.0003562432390699621</v>
       </c>
       <c r="D11">
-        <v>-0.00307680256172882</v>
+        <v>0.001734709694305225</v>
       </c>
       <c r="E11">
-        <v>0.05517083977525238</v>
+        <v>0.03605590663396419</v>
       </c>
       <c r="F11">
-        <v>-0.1221031027414574</v>
+        <v>-0.104449111287138</v>
       </c>
       <c r="G11">
-        <v>0.1787505468142071</v>
+        <v>0.1015225232062136</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -714,19 +708,19 @@
         <v>125</v>
       </c>
       <c r="C12">
-        <v>0.005285064335128388</v>
+        <v>-0.001515966472595225</v>
       </c>
       <c r="D12">
-        <v>-0.002659510167666634</v>
+        <v>-0.00307680256172882</v>
       </c>
       <c r="E12">
-        <v>0.06830666836887615</v>
+        <v>0.05479918535013117</v>
       </c>
       <c r="F12">
-        <v>-0.1496912439695927</v>
+        <v>-0.1221031027414574</v>
       </c>
       <c r="G12">
-        <v>0.2984478960867282</v>
+        <v>0.1787505468142071</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -737,19 +731,19 @@
         <v>125</v>
       </c>
       <c r="C13">
-        <v>0.01133121375920442</v>
+        <v>0.005570799893693436</v>
       </c>
       <c r="D13">
-        <v>0.01630808802667353</v>
+        <v>-0.002659510167666634</v>
       </c>
       <c r="E13">
-        <v>0.09027518276497754</v>
+        <v>0.06852829894537391</v>
       </c>
       <c r="F13">
-        <v>-0.3796172008132213</v>
+        <v>-0.1496912439695927</v>
       </c>
       <c r="G13">
-        <v>0.2110244452016588</v>
+        <v>0.2984478960867282</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -757,22 +751,22 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="C14">
-        <v>0.05552097327060793</v>
+        <v>0.01141388919032527</v>
       </c>
       <c r="D14">
-        <v>0.05285051494697646</v>
+        <v>0.01662276108761829</v>
       </c>
       <c r="E14">
-        <v>0.1761753199412623</v>
+        <v>0.09048337220893307</v>
       </c>
       <c r="F14">
-        <v>-0.6048027444253857</v>
+        <v>-0.3796172008132213</v>
       </c>
       <c r="G14">
-        <v>0.5139952652833859</v>
+        <v>0.2197523099509714</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -780,22 +774,22 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="C15">
-        <v>0.08295627658393388</v>
+        <v>0.09753266661330695</v>
       </c>
       <c r="D15">
-        <v>0.06093127921066355</v>
+        <v>0.03554055337672213</v>
       </c>
       <c r="E15">
-        <v>0.2474999558708884</v>
+        <v>0.2328680729859484</v>
       </c>
       <c r="F15">
-        <v>-0.6850771869639791</v>
+        <v>-0.433768397667315</v>
       </c>
       <c r="G15">
-        <v>0.8150211205495967</v>
+        <v>0.4382903435752072</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -803,22 +797,22 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="C16">
-        <v>0.04452940841308847</v>
+        <v>-0.0009259959478472051</v>
       </c>
       <c r="D16">
-        <v>0.06630384650956667</v>
+        <v>-0.000663346225892758</v>
       </c>
       <c r="E16">
-        <v>0.354859442673206</v>
+        <v>0.02988337221502036</v>
       </c>
       <c r="F16">
-        <v>-0.8055555555555558</v>
+        <v>-0.0904645956360296</v>
       </c>
       <c r="G16">
-        <v>0.9899062725306409</v>
+        <v>0.07815541631816372</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -826,22 +820,22 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C17">
-        <v>0.0004905706210143237</v>
+        <v>0.00238139979255795</v>
       </c>
       <c r="D17">
-        <v>6.848541734405522E-05</v>
+        <v>0.001863401078549604</v>
       </c>
       <c r="E17">
-        <v>0.03077679795987784</v>
+        <v>0.05606974890765763</v>
       </c>
       <c r="F17">
-        <v>-0.0904645956360296</v>
+        <v>-0.1539596832972503</v>
       </c>
       <c r="G17">
-        <v>0.08006082765098969</v>
+        <v>0.1285087530406699</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -849,22 +843,22 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C18">
-        <v>0.004446452537794658</v>
+        <v>0.01140953665531187</v>
       </c>
       <c r="D18">
-        <v>0.003283214589403283</v>
+        <v>0.008978825756346676</v>
       </c>
       <c r="E18">
-        <v>0.056710277108899</v>
+        <v>0.06390773742077208</v>
       </c>
       <c r="F18">
-        <v>-0.1539596832972503</v>
+        <v>-0.1602402713514575</v>
       </c>
       <c r="G18">
-        <v>0.1285087530406699</v>
+        <v>0.2984478960867282</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -872,22 +866,22 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C19">
-        <v>0.01301030067761407</v>
+        <v>0.004984469649769689</v>
       </c>
       <c r="D19">
-        <v>0.009626216367549012</v>
+        <v>0.01042813733014381</v>
       </c>
       <c r="E19">
-        <v>0.06435343875393279</v>
+        <v>0.1036470008998143</v>
       </c>
       <c r="F19">
-        <v>-0.1602402713514575</v>
+        <v>-0.3796172008132213</v>
       </c>
       <c r="G19">
-        <v>0.2984478960867282</v>
+        <v>0.3774921013880268</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -895,22 +889,22 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="C20">
-        <v>0.006266923758522714</v>
+        <v>0.02444790427551347</v>
       </c>
       <c r="D20">
-        <v>0.01633579943917263</v>
+        <v>0.03487424585320698</v>
       </c>
       <c r="E20">
-        <v>0.1025213646854223</v>
+        <v>0.1632272141793066</v>
       </c>
       <c r="F20">
-        <v>-0.3796172008132213</v>
+        <v>-0.433768397667315</v>
       </c>
       <c r="G20">
-        <v>0.3774921013880268</v>
+        <v>0.4080081424909723</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -918,22 +912,22 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>97</v>
+        <v>6</v>
       </c>
       <c r="C21">
-        <v>0.04724645054018276</v>
+        <v>0.144464350765866</v>
       </c>
       <c r="D21">
-        <v>0.05088738302678308</v>
+        <v>0.1058445622820093</v>
       </c>
       <c r="E21">
-        <v>0.1368794941840714</v>
+        <v>0.1666214690230211</v>
       </c>
       <c r="F21">
-        <v>-0.433768397667315</v>
+        <v>0.001090850260743625</v>
       </c>
       <c r="G21">
-        <v>0.5139952652833859</v>
+        <v>0.4687475454211276</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -941,22 +935,22 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="C22">
-        <v>0.07340772866018906</v>
+        <v>0.01807559469166843</v>
       </c>
       <c r="D22">
-        <v>0.0583676728098067</v>
+        <v>0.01765002735433061</v>
       </c>
       <c r="E22">
-        <v>0.2278209518000659</v>
+        <v>0.09633877717722504</v>
       </c>
       <c r="F22">
-        <v>-0.7570694464836296</v>
+        <v>-0.2209056424683098</v>
       </c>
       <c r="G22">
-        <v>0.8150211205495967</v>
+        <v>0.232188158889771</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -964,22 +958,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="C23">
-        <v>0.004000556722088157</v>
+        <v>0.02294005261910105</v>
       </c>
       <c r="D23">
-        <v>0.0631910442994329</v>
+        <v>0.02064875502047747</v>
       </c>
       <c r="E23">
-        <v>0.3564992576223297</v>
+        <v>0.09716245359691413</v>
       </c>
       <c r="F23">
-        <v>-0.7673872760963555</v>
+        <v>-0.2273202447413781</v>
       </c>
       <c r="G23">
-        <v>0.7817603911980466</v>
+        <v>0.2662848034600641</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -990,19 +984,19 @@
         <v>124</v>
       </c>
       <c r="C24">
-        <v>0.01816274659278014</v>
+        <v>0.002173359413271701</v>
       </c>
       <c r="D24">
-        <v>0.01718278148113486</v>
+        <v>0.003774908394451271</v>
       </c>
       <c r="E24">
-        <v>0.0965209194141894</v>
+        <v>0.03731927598461233</v>
       </c>
       <c r="F24">
-        <v>-0.2209056424683098</v>
+        <v>-0.104449111287138</v>
       </c>
       <c r="G24">
-        <v>0.232188158889771</v>
+        <v>0.08250685134647584</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1013,19 +1007,19 @@
         <v>124</v>
       </c>
       <c r="C25">
-        <v>0.02289898046432037</v>
+        <v>0.003197199375058779</v>
       </c>
       <c r="D25">
-        <v>0.02064875502047747</v>
+        <v>0.004457474237063139</v>
       </c>
       <c r="E25">
-        <v>0.09711258332539809</v>
+        <v>0.05405633512964923</v>
       </c>
       <c r="F25">
-        <v>-0.2273202447413781</v>
+        <v>-0.1221031027414574</v>
       </c>
       <c r="G25">
-        <v>0.2662848034600641</v>
+        <v>0.1088786277829172</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1033,22 +1027,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C26">
-        <v>0.002172341655948481</v>
+        <v>-0.001199623914782526</v>
       </c>
       <c r="D26">
-        <v>0.003774908394451271</v>
+        <v>-0.0006057405594949716</v>
       </c>
       <c r="E26">
-        <v>0.0373193899672749</v>
+        <v>0.03930384389704746</v>
       </c>
       <c r="F26">
         <v>-0.104449111287138</v>
       </c>
       <c r="G26">
-        <v>0.08250685134647584</v>
+        <v>0.08239107533804257</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1056,67 +1050,21 @@
         <v>32</v>
       </c>
       <c r="B27">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C27">
-        <v>0.003194690470211211</v>
+        <v>-0.001429053484884809</v>
       </c>
       <c r="D27">
-        <v>0.004383650961968937</v>
+        <v>0.004428975769990795</v>
       </c>
       <c r="E27">
-        <v>0.05405252694445439</v>
+        <v>0.06353852713077812</v>
       </c>
       <c r="F27">
-        <v>-0.1221031027414574</v>
+        <v>-0.2596941469973632</v>
       </c>
       <c r="G27">
-        <v>0.1088786277829172</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28">
-        <v>126</v>
-      </c>
-      <c r="C28">
-        <v>-0.001213900410916014</v>
-      </c>
-      <c r="D28">
-        <v>-0.0006057405594949716</v>
-      </c>
-      <c r="E28">
-        <v>0.03930786467249857</v>
-      </c>
-      <c r="F28">
-        <v>-0.104449111287138</v>
-      </c>
-      <c r="G28">
-        <v>0.08239107533804257</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29">
-        <v>126</v>
-      </c>
-      <c r="C29">
-        <v>-0.001460098561881292</v>
-      </c>
-      <c r="D29">
-        <v>0.004428975769990795</v>
-      </c>
-      <c r="E29">
-        <v>0.06354472312450485</v>
-      </c>
-      <c r="F29">
-        <v>-0.2596941469973632</v>
-      </c>
-      <c r="G29">
         <v>0.1285087530406699</v>
       </c>
     </row>

--- a/out/thesis/tables/summary_statistics.xlsx
+++ b/out/thesis/tables/summary_statistics.xlsx
@@ -43,6 +43,9 @@
     <t>CAR_ANN_INTRADAY_30M</t>
   </si>
   <si>
+    <t>CAR_ANN_INTRADAY_M60_P180</t>
+  </si>
+  <si>
     <t>CAR_ANN_INTRADAY_1H</t>
   </si>
   <si>
@@ -74,9 +77,6 @@
   </si>
   <si>
     <t>CAR_ANN_10_10</t>
-  </si>
-  <si>
-    <t>BHAR_ANN_60</t>
   </si>
   <si>
     <t>CAR_CLOSE_1_1</t>
@@ -475,19 +475,19 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C2">
-        <v>0.001199727994858157</v>
+        <v>-0.002078193354837277</v>
       </c>
       <c r="D2">
-        <v>0.0001032200883013812</v>
+        <v>8.07655248691112E-05</v>
       </c>
       <c r="E2">
-        <v>0.006146008555622823</v>
+        <v>0.01922384175885325</v>
       </c>
       <c r="F2">
-        <v>-0.01057432171809979</v>
+        <v>-0.102054794520548</v>
       </c>
       <c r="G2">
         <v>0.0362517880771814</v>
@@ -498,19 +498,19 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C3">
-        <v>-9.566207374977578E-05</v>
+        <v>-0.003417212874368534</v>
       </c>
       <c r="D3">
-        <v>0.0002336781725555482</v>
+        <v>8.462543222417991E-06</v>
       </c>
       <c r="E3">
-        <v>0.007379119416778246</v>
+        <v>0.01986503522406245</v>
       </c>
       <c r="F3">
-        <v>-0.02451359356489838</v>
+        <v>-0.1047245122932406</v>
       </c>
       <c r="G3">
         <v>0.02739300227640433</v>
@@ -521,22 +521,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C4">
-        <v>0.0004584012071024731</v>
+        <v>-0.003231069893909831</v>
       </c>
       <c r="D4">
-        <v>-0.0001536537933449688</v>
+        <v>0.00172614520468321</v>
       </c>
       <c r="E4">
-        <v>0.007309138163196068</v>
+        <v>0.03128071273806435</v>
       </c>
       <c r="F4">
-        <v>-0.02435155633461674</v>
+        <v>-0.1490501363145055</v>
       </c>
       <c r="G4">
-        <v>0.01725191826223654</v>
+        <v>0.08592058768238695</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -544,22 +544,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C5">
-        <v>0.0003559423720667383</v>
+        <v>-0.003403930815966738</v>
       </c>
       <c r="D5">
-        <v>0.000414140879612637</v>
+        <v>-0.0003687083847000687</v>
       </c>
       <c r="E5">
-        <v>0.01398584412829094</v>
+        <v>0.02267213547530057</v>
       </c>
       <c r="F5">
-        <v>-0.04243076464411492</v>
+        <v>-0.1212050575195777</v>
       </c>
       <c r="G5">
-        <v>0.06166508047730938</v>
+        <v>0.01725191826223654</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -567,22 +567,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C6">
-        <v>0.004379907928898975</v>
+        <v>-0.004387107744967301</v>
       </c>
       <c r="D6">
-        <v>0.004567992705071912</v>
+        <v>0.0003450791432288621</v>
       </c>
       <c r="E6">
-        <v>0.04492360948754695</v>
+        <v>0.02977423161107267</v>
       </c>
       <c r="F6">
-        <v>-0.1070767147920283</v>
+        <v>-0.1490501363145055</v>
       </c>
       <c r="G6">
-        <v>0.1511130395694213</v>
+        <v>0.06166508047730938</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -590,22 +590,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C7">
-        <v>0.002193531755543433</v>
+        <v>0.0002700488514069686</v>
       </c>
       <c r="D7">
-        <v>0.0006039455622826873</v>
+        <v>0.004313082069451687</v>
       </c>
       <c r="E7">
-        <v>0.02542904183886424</v>
+        <v>0.04976457246757165</v>
       </c>
       <c r="F7">
-        <v>-0.05843128444713655</v>
+        <v>-0.1250806530120993</v>
       </c>
       <c r="G7">
-        <v>0.1179295218626863</v>
+        <v>0.1511130395694213</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -613,22 +613,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C8">
-        <v>-0.0008937873069912753</v>
+        <v>-0.002607854532394627</v>
       </c>
       <c r="D8">
-        <v>-0.00111006197305249</v>
+        <v>0.0003450791432288621</v>
       </c>
       <c r="E8">
-        <v>0.007337127077800328</v>
+        <v>0.03660933818936198</v>
       </c>
       <c r="F8">
-        <v>-0.02891229898386977</v>
+        <v>-0.1490501363145055</v>
       </c>
       <c r="G8">
-        <v>0.02668975077741524</v>
+        <v>0.1179295218626863</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -636,22 +636,22 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C9">
-        <v>0.002120267944568103</v>
+        <v>-0.0001976817575056889</v>
       </c>
       <c r="D9">
-        <v>0.003933654681129604</v>
+        <v>-0.00100294181823566</v>
       </c>
       <c r="E9">
-        <v>0.02349017831573549</v>
+        <v>0.008192338776425334</v>
       </c>
       <c r="F9">
-        <v>-0.05740627791566398</v>
+        <v>-0.02891229898386977</v>
       </c>
       <c r="G9">
-        <v>0.06906627810122822</v>
+        <v>0.02668975077741524</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -659,22 +659,22 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C10">
-        <v>17.96630035866757</v>
+        <v>0.002813893828943917</v>
       </c>
       <c r="D10">
-        <v>8.819130144622921</v>
+        <v>0.004421847840168082</v>
       </c>
       <c r="E10">
-        <v>121.7119859414391</v>
+        <v>0.02342860627356884</v>
       </c>
       <c r="F10">
-        <v>-144.4830120544106</v>
+        <v>-0.05740627791566398</v>
       </c>
       <c r="G10">
-        <v>622.0153206002653</v>
+        <v>0.06906627810122822</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -682,22 +682,22 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>125</v>
+        <v>63</v>
       </c>
       <c r="C11">
-        <v>0.0003562432390699621</v>
+        <v>19.97747538752922</v>
       </c>
       <c r="D11">
-        <v>0.001734709694305225</v>
+        <v>11.95413488410556</v>
       </c>
       <c r="E11">
-        <v>0.03605590663396419</v>
+        <v>120.2551442491456</v>
       </c>
       <c r="F11">
-        <v>-0.104449111287138</v>
+        <v>-144.4830120544106</v>
       </c>
       <c r="G11">
-        <v>0.1015225232062136</v>
+        <v>622.0153206002653</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -708,19 +708,19 @@
         <v>125</v>
       </c>
       <c r="C12">
-        <v>-0.001515966472595225</v>
+        <v>0.0003562432390699621</v>
       </c>
       <c r="D12">
-        <v>-0.00307680256172882</v>
+        <v>0.001734709694305225</v>
       </c>
       <c r="E12">
-        <v>0.05479918535013117</v>
+        <v>0.03605590663396419</v>
       </c>
       <c r="F12">
-        <v>-0.1221031027414574</v>
+        <v>-0.104449111287138</v>
       </c>
       <c r="G12">
-        <v>0.1787505468142071</v>
+        <v>0.1015225232062136</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -731,19 +731,19 @@
         <v>125</v>
       </c>
       <c r="C13">
-        <v>0.005570799893693436</v>
+        <v>-0.001515966472595225</v>
       </c>
       <c r="D13">
-        <v>-0.002659510167666634</v>
+        <v>-0.00307680256172882</v>
       </c>
       <c r="E13">
-        <v>0.06852829894537391</v>
+        <v>0.05479918535013117</v>
       </c>
       <c r="F13">
-        <v>-0.1496912439695927</v>
+        <v>-0.1221031027414574</v>
       </c>
       <c r="G13">
-        <v>0.2984478960867282</v>
+        <v>0.1787505468142071</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -754,19 +754,19 @@
         <v>125</v>
       </c>
       <c r="C14">
-        <v>0.01141388919032527</v>
+        <v>0.005570799893693436</v>
       </c>
       <c r="D14">
-        <v>0.01662276108761829</v>
+        <v>-0.002659510167666634</v>
       </c>
       <c r="E14">
-        <v>0.09048337220893307</v>
+        <v>0.06852829894537391</v>
       </c>
       <c r="F14">
-        <v>-0.3796172008132213</v>
+        <v>-0.1496912439695927</v>
       </c>
       <c r="G14">
-        <v>0.2197523099509714</v>
+        <v>0.2984478960867282</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -774,22 +774,22 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="C15">
-        <v>0.09753266661330695</v>
+        <v>0.01102386544064671</v>
       </c>
       <c r="D15">
-        <v>0.03554055337672213</v>
+        <v>0.01603369536199883</v>
       </c>
       <c r="E15">
-        <v>0.2328680729859484</v>
+        <v>0.09053717623051984</v>
       </c>
       <c r="F15">
-        <v>-0.433768397667315</v>
+        <v>-0.3796172008132213</v>
       </c>
       <c r="G15">
-        <v>0.4382903435752072</v>
+        <v>0.2197523099509714</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -797,19 +797,19 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C16">
-        <v>-0.0009259959478472051</v>
+        <v>-0.0006033777277797611</v>
       </c>
       <c r="D16">
-        <v>-0.000663346225892758</v>
+        <v>6.848541734405522E-05</v>
       </c>
       <c r="E16">
-        <v>0.02988337221502036</v>
+        <v>0.03501176319123906</v>
       </c>
       <c r="F16">
-        <v>-0.0904645956360296</v>
+        <v>-0.1641781035903104</v>
       </c>
       <c r="G16">
         <v>0.07815541631816372</v>
@@ -820,16 +820,16 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C17">
-        <v>0.00238139979255795</v>
+        <v>0.003239123481441927</v>
       </c>
       <c r="D17">
-        <v>0.001863401078549604</v>
+        <v>0.003283214589403283</v>
       </c>
       <c r="E17">
-        <v>0.05606974890765763</v>
+        <v>0.05777557742315756</v>
       </c>
       <c r="F17">
         <v>-0.1539596832972503</v>
@@ -843,16 +843,16 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C18">
-        <v>0.01140953665531187</v>
+        <v>0.01104106361583274</v>
       </c>
       <c r="D18">
-        <v>0.008978825756346676</v>
+        <v>0.009354139825523911</v>
       </c>
       <c r="E18">
-        <v>0.06390773742077208</v>
+        <v>0.06586314724511141</v>
       </c>
       <c r="F18">
         <v>-0.1602402713514575</v>
@@ -866,16 +866,16 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C19">
-        <v>0.004984469649769689</v>
+        <v>0.005065025401463818</v>
       </c>
       <c r="D19">
-        <v>0.01042813733014381</v>
+        <v>0.01479023301505315</v>
       </c>
       <c r="E19">
-        <v>0.1036470008998143</v>
+        <v>0.1031439368896857</v>
       </c>
       <c r="F19">
         <v>-0.3796172008132213</v>
@@ -889,19 +889,19 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C20">
-        <v>0.02444790427551347</v>
+        <v>0.09964812691641563</v>
       </c>
       <c r="D20">
-        <v>0.03487424585320698</v>
+        <v>0.04278571085956895</v>
       </c>
       <c r="E20">
-        <v>0.1632272141793066</v>
+        <v>0.1530572164856446</v>
       </c>
       <c r="F20">
-        <v>-0.433768397667315</v>
+        <v>-0.003701838924994982</v>
       </c>
       <c r="G20">
         <v>0.4080081424909723</v>
@@ -912,22 +912,22 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>0.144464350765866</v>
+        <v>0.2580809782148668</v>
       </c>
       <c r="D21">
-        <v>0.1058445622820093</v>
+        <v>0.2580809782148668</v>
       </c>
       <c r="E21">
-        <v>0.1666214690230211</v>
+        <v>0.1997952681993614</v>
       </c>
       <c r="F21">
-        <v>0.001090850260743625</v>
+        <v>0.1168043892221133</v>
       </c>
       <c r="G21">
-        <v>0.4687475454211276</v>
+        <v>0.3993575672076202</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1027,19 +1027,19 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C26">
-        <v>-0.001199623914782526</v>
+        <v>-0.000506522846464162</v>
       </c>
       <c r="D26">
-        <v>-0.0006057405594949716</v>
+        <v>0.0002537611966281217</v>
       </c>
       <c r="E26">
-        <v>0.03930384389704746</v>
+        <v>0.0380604321393923</v>
       </c>
       <c r="F26">
-        <v>-0.104449111287138</v>
+        <v>-0.1641781035903104</v>
       </c>
       <c r="G26">
         <v>0.08239107533804257</v>
@@ -1050,19 +1050,19 @@
         <v>32</v>
       </c>
       <c r="B27">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C27">
-        <v>-0.001429053484884809</v>
+        <v>0.003976883696962459</v>
       </c>
       <c r="D27">
-        <v>0.004428975769990795</v>
+        <v>0.003900615782771196</v>
       </c>
       <c r="E27">
-        <v>0.06353852713077812</v>
+        <v>0.05790452551676187</v>
       </c>
       <c r="F27">
-        <v>-0.2596941469973632</v>
+        <v>-0.1539596832972503</v>
       </c>
       <c r="G27">
         <v>0.1285087530406699</v>

--- a/out/thesis/tables/summary_statistics.xlsx
+++ b/out/thesis/tables/summary_statistics.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>metric</t>
   </si>
@@ -79,6 +79,24 @@
     <t>CAR_ANN_10_10</t>
   </si>
   <si>
+    <t>CAR_ANN_30_30</t>
+  </si>
+  <si>
+    <t>CAR_ANN_50_50</t>
+  </si>
+  <si>
+    <t>CAR_ANN_30_5</t>
+  </si>
+  <si>
+    <t>BHAR_ANN_60</t>
+  </si>
+  <si>
+    <t>BHAR_ANN_120</t>
+  </si>
+  <si>
+    <t>BHAR_ANN_250</t>
+  </si>
+  <si>
     <t>CAR_CLOSE_1_1</t>
   </si>
   <si>
@@ -97,22 +115,52 @@
     <t>BHAR_CLOSE_120</t>
   </si>
   <si>
+    <t>BHAR_CLOSE_250</t>
+  </si>
+  <si>
     <t>RUNUP_PRE_30_5</t>
   </si>
   <si>
     <t>CAR_PRE_ANNOUNCEMENT</t>
   </si>
   <si>
+    <t>DIFF_CAR_ANN_MINUS_CREATE_1_1</t>
+  </si>
+  <si>
     <t>CAR_CREATE_1_1</t>
   </si>
   <si>
     <t>CAR_CREATE_3_3</t>
   </si>
   <si>
+    <t>CAR_CREATE_30_5</t>
+  </si>
+  <si>
+    <t>CAR_ACT_30_30</t>
+  </si>
+  <si>
+    <t>CAR_ACT_50_50</t>
+  </si>
+  <si>
+    <t>CAR_ACT_30_5</t>
+  </si>
+  <si>
+    <t>CAR_CREATE_30_30</t>
+  </si>
+  <si>
+    <t>CAR_CREATE_50_50</t>
+  </si>
+  <si>
     <t>CAR_ACT_1_1</t>
   </si>
   <si>
     <t>CAR_ACT_3_3</t>
+  </si>
+  <si>
+    <t>DIFF_CAR_ANN_CREATE_1_1</t>
+  </si>
+  <si>
+    <t>DIFF_CAR_ANN_CREATE_30_5</t>
   </si>
 </sst>
 </file>
@@ -444,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -777,13 +825,13 @@
         <v>125</v>
       </c>
       <c r="C15">
-        <v>0.01102386544064671</v>
+        <v>0.01141388919032527</v>
       </c>
       <c r="D15">
-        <v>0.01603369536199883</v>
+        <v>0.01662276108761829</v>
       </c>
       <c r="E15">
-        <v>0.09053717623051984</v>
+        <v>0.09048337220893307</v>
       </c>
       <c r="F15">
         <v>-0.3796172008132213</v>
@@ -797,22 +845,22 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="C16">
-        <v>-0.0006033777277797611</v>
+        <v>0.03840210554338377</v>
       </c>
       <c r="D16">
-        <v>6.848541734405522E-05</v>
+        <v>0.04378251396259564</v>
       </c>
       <c r="E16">
-        <v>0.03501176319123906</v>
+        <v>0.1472498877080011</v>
       </c>
       <c r="F16">
-        <v>-0.1641781035903104</v>
+        <v>-0.4009498331069936</v>
       </c>
       <c r="G16">
-        <v>0.07815541631816372</v>
+        <v>0.5955206822891433</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -820,22 +868,22 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="C17">
-        <v>0.003239123481441927</v>
+        <v>0.05894287004584058</v>
       </c>
       <c r="D17">
-        <v>0.003283214589403283</v>
+        <v>0.04516389215826493</v>
       </c>
       <c r="E17">
-        <v>0.05777557742315756</v>
+        <v>0.215678505435691</v>
       </c>
       <c r="F17">
-        <v>-0.1539596832972503</v>
+        <v>-0.8486976398408415</v>
       </c>
       <c r="G17">
-        <v>0.1285087530406699</v>
+        <v>0.620081894144962</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -843,22 +891,22 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="C18">
-        <v>0.01104106361583274</v>
+        <v>0.01807559469166843</v>
       </c>
       <c r="D18">
-        <v>0.009354139825523911</v>
+        <v>0.01765002735433061</v>
       </c>
       <c r="E18">
-        <v>0.06586314724511141</v>
+        <v>0.09633877717722504</v>
       </c>
       <c r="F18">
-        <v>-0.1602402713514575</v>
+        <v>-0.2209056424683098</v>
       </c>
       <c r="G18">
-        <v>0.2984478960867282</v>
+        <v>0.232188158889771</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -866,22 +914,22 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="C19">
-        <v>0.005065025401463818</v>
+        <v>0.02938113122092688</v>
       </c>
       <c r="D19">
-        <v>0.01479023301505315</v>
+        <v>0.01832886245939636</v>
       </c>
       <c r="E19">
-        <v>0.1031439368896857</v>
+        <v>0.1910392495250928</v>
       </c>
       <c r="F19">
-        <v>-0.3796172008132213</v>
+        <v>-0.433768397667315</v>
       </c>
       <c r="G19">
-        <v>0.3774921013880268</v>
+        <v>0.4382903435752072</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -889,22 +937,22 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C20">
-        <v>0.09964812691641563</v>
+        <v>0.04681414714363292</v>
       </c>
       <c r="D20">
-        <v>0.04278571085956895</v>
+        <v>0.03751782572927659</v>
       </c>
       <c r="E20">
-        <v>0.1530572164856446</v>
+        <v>0.1587931297127634</v>
       </c>
       <c r="F20">
-        <v>-0.003701838924994982</v>
+        <v>-0.2146116371107395</v>
       </c>
       <c r="G20">
-        <v>0.4080081424909723</v>
+        <v>0.3955800480086653</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -912,22 +960,22 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C21">
-        <v>0.2580809782148668</v>
+        <v>0.09822753841660853</v>
       </c>
       <c r="D21">
-        <v>0.2580809782148668</v>
+        <v>0.1585172071302531</v>
       </c>
       <c r="E21">
-        <v>0.1997952681993614</v>
+        <v>0.214961570489835</v>
       </c>
       <c r="F21">
-        <v>0.1168043892221133</v>
+        <v>-0.3137868593984369</v>
       </c>
       <c r="G21">
-        <v>0.3993575672076202</v>
+        <v>0.5058103389931563</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -935,22 +983,22 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="C22">
-        <v>0.01807559469166843</v>
+        <v>-0.0006033777277797611</v>
       </c>
       <c r="D22">
-        <v>0.01765002735433061</v>
+        <v>6.848541734405522E-05</v>
       </c>
       <c r="E22">
-        <v>0.09633877717722504</v>
+        <v>0.03501176319123906</v>
       </c>
       <c r="F22">
-        <v>-0.2209056424683098</v>
+        <v>-0.1641781035903104</v>
       </c>
       <c r="G22">
-        <v>0.232188158889771</v>
+        <v>0.07815541631816372</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -958,22 +1006,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="C23">
-        <v>0.02294005261910105</v>
+        <v>0.003239123481441927</v>
       </c>
       <c r="D23">
-        <v>0.02064875502047747</v>
+        <v>0.003283214589403283</v>
       </c>
       <c r="E23">
-        <v>0.09716245359691413</v>
+        <v>0.05777557742315756</v>
       </c>
       <c r="F23">
-        <v>-0.2273202447413781</v>
+        <v>-0.1539596832972503</v>
       </c>
       <c r="G23">
-        <v>0.2662848034600641</v>
+        <v>0.1285087530406699</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -981,22 +1029,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="C24">
-        <v>0.002173359413271701</v>
+        <v>0.01117910734539273</v>
       </c>
       <c r="D24">
-        <v>0.003774908394451271</v>
+        <v>0.009354139825523911</v>
       </c>
       <c r="E24">
-        <v>0.03731927598461233</v>
+        <v>0.06570302063611493</v>
       </c>
       <c r="F24">
-        <v>-0.104449111287138</v>
+        <v>-0.1602402713514575</v>
       </c>
       <c r="G24">
-        <v>0.08250685134647584</v>
+        <v>0.2984478960867282</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1004,22 +1052,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="C25">
-        <v>0.003197199375058779</v>
+        <v>0.002787607160732627</v>
       </c>
       <c r="D25">
-        <v>0.004457474237063139</v>
+        <v>0.01042813733014381</v>
       </c>
       <c r="E25">
-        <v>0.05405633512964923</v>
+        <v>0.1054898129766568</v>
       </c>
       <c r="F25">
-        <v>-0.1221031027414574</v>
+        <v>-0.3796172008132213</v>
       </c>
       <c r="G25">
-        <v>0.1088786277829172</v>
+        <v>0.3774921013880268</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1027,22 +1075,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="C26">
-        <v>-0.000506522846464162</v>
+        <v>0.02906863230679001</v>
       </c>
       <c r="D26">
-        <v>0.0002537611966281217</v>
+        <v>0.03864708717533516</v>
       </c>
       <c r="E26">
-        <v>0.0380604321393923</v>
+        <v>0.1593585182948327</v>
       </c>
       <c r="F26">
-        <v>-0.1641781035903104</v>
+        <v>-0.433768397667315</v>
       </c>
       <c r="G26">
-        <v>0.08239107533804257</v>
+        <v>0.4080081424909723</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1050,22 +1098,390 @@
         <v>32</v>
       </c>
       <c r="B27">
+        <v>15</v>
+      </c>
+      <c r="C27">
+        <v>0.08327223382481209</v>
+      </c>
+      <c r="D27">
+        <v>0.1151189645836597</v>
+      </c>
+      <c r="E27">
+        <v>0.1472924710738844</v>
+      </c>
+      <c r="F27">
+        <v>-0.2146116371107395</v>
+      </c>
+      <c r="G27">
+        <v>0.4687475454211276</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28">
+        <v>12</v>
+      </c>
+      <c r="C28">
+        <v>0.1070447241933858</v>
+      </c>
+      <c r="D28">
+        <v>0.1490642604953996</v>
+      </c>
+      <c r="E28">
+        <v>0.2021190278347268</v>
+      </c>
+      <c r="F28">
+        <v>-0.3137868593984369</v>
+      </c>
+      <c r="G28">
+        <v>0.4803698517530059</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29">
         <v>124</v>
       </c>
-      <c r="C27">
+      <c r="C29">
+        <v>0.01807559469166843</v>
+      </c>
+      <c r="D29">
+        <v>0.01765002735433061</v>
+      </c>
+      <c r="E29">
+        <v>0.09633877717722504</v>
+      </c>
+      <c r="F29">
+        <v>-0.2209056424683098</v>
+      </c>
+      <c r="G29">
+        <v>0.232188158889771</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30">
+        <v>124</v>
+      </c>
+      <c r="C30">
+        <v>0.02294005261910105</v>
+      </c>
+      <c r="D30">
+        <v>0.02064875502047747</v>
+      </c>
+      <c r="E30">
+        <v>0.09716245359691413</v>
+      </c>
+      <c r="F30">
+        <v>-0.2273202447413781</v>
+      </c>
+      <c r="G30">
+        <v>0.2662848034600641</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31">
+        <v>124</v>
+      </c>
+      <c r="C31">
+        <v>-0.001843891212568493</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0.0309216972859208</v>
+      </c>
+      <c r="F31">
+        <v>-0.1180550669313547</v>
+      </c>
+      <c r="G31">
+        <v>0.1328140243405103</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32">
+        <v>124</v>
+      </c>
+      <c r="C32">
+        <v>0.002173359413271701</v>
+      </c>
+      <c r="D32">
+        <v>0.003774908394451271</v>
+      </c>
+      <c r="E32">
+        <v>0.03731927598461233</v>
+      </c>
+      <c r="F32">
+        <v>-0.104449111287138</v>
+      </c>
+      <c r="G32">
+        <v>0.08250685134647584</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33">
+        <v>124</v>
+      </c>
+      <c r="C33">
+        <v>0.003197199375058779</v>
+      </c>
+      <c r="D33">
+        <v>0.004457474237063139</v>
+      </c>
+      <c r="E33">
+        <v>0.05405633512964923</v>
+      </c>
+      <c r="F33">
+        <v>-0.1221031027414574</v>
+      </c>
+      <c r="G33">
+        <v>0.1088786277829172</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34">
+        <v>123</v>
+      </c>
+      <c r="C34">
+        <v>0.01517675200557212</v>
+      </c>
+      <c r="D34">
+        <v>0.02163365373883284</v>
+      </c>
+      <c r="E34">
+        <v>0.09012583573771463</v>
+      </c>
+      <c r="F34">
+        <v>-0.2209056424683098</v>
+      </c>
+      <c r="G34">
+        <v>0.2261718080023797</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35">
+        <v>124</v>
+      </c>
+      <c r="C35">
+        <v>0.03313518239140669</v>
+      </c>
+      <c r="D35">
+        <v>0.0453380604387274</v>
+      </c>
+      <c r="E35">
+        <v>0.1471717443705267</v>
+      </c>
+      <c r="F35">
+        <v>-0.4009498331069936</v>
+      </c>
+      <c r="G35">
+        <v>0.6945373571790375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36">
+        <v>124</v>
+      </c>
+      <c r="C36">
+        <v>0.06310926996856751</v>
+      </c>
+      <c r="D36">
+        <v>0.06218833736899276</v>
+      </c>
+      <c r="E36">
+        <v>0.1785908691824007</v>
+      </c>
+      <c r="F36">
+        <v>-0.8486976398408415</v>
+      </c>
+      <c r="G36">
+        <v>0.620081894144962</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37">
+        <v>124</v>
+      </c>
+      <c r="C37">
+        <v>0.006534547239817555</v>
+      </c>
+      <c r="D37">
+        <v>0.004596198034364563</v>
+      </c>
+      <c r="E37">
+        <v>0.09163025142845681</v>
+      </c>
+      <c r="F37">
+        <v>-0.2019606657366456</v>
+      </c>
+      <c r="G37">
+        <v>0.2549786978652205</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38">
+        <v>123</v>
+      </c>
+      <c r="C38">
+        <v>0.04121771303062292</v>
+      </c>
+      <c r="D38">
+        <v>0.0476745437488596</v>
+      </c>
+      <c r="E38">
+        <v>0.1302844520320303</v>
+      </c>
+      <c r="F38">
+        <v>-0.4009498331069936</v>
+      </c>
+      <c r="G38">
+        <v>0.292456623955862</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39">
+        <v>123</v>
+      </c>
+      <c r="C39">
+        <v>0.05335605611127209</v>
+      </c>
+      <c r="D39">
+        <v>0.05997559025975518</v>
+      </c>
+      <c r="E39">
+        <v>0.2013012073715446</v>
+      </c>
+      <c r="F39">
+        <v>-0.8486976398408415</v>
+      </c>
+      <c r="G39">
+        <v>0.620081894144962</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40">
+        <v>124</v>
+      </c>
+      <c r="C40">
+        <v>-0.000506522846464162</v>
+      </c>
+      <c r="D40">
+        <v>0.0002537611966281217</v>
+      </c>
+      <c r="E40">
+        <v>0.0380604321393923</v>
+      </c>
+      <c r="F40">
+        <v>-0.1641781035903104</v>
+      </c>
+      <c r="G40">
+        <v>0.08239107533804257</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41">
+        <v>124</v>
+      </c>
+      <c r="C41">
         <v>0.003976883696962459</v>
       </c>
-      <c r="D27">
+      <c r="D41">
         <v>0.003900615782771196</v>
       </c>
-      <c r="E27">
+      <c r="E41">
         <v>0.05790452551676187</v>
       </c>
-      <c r="F27">
+      <c r="F41">
         <v>-0.1539596832972503</v>
       </c>
-      <c r="G27">
+      <c r="G41">
         <v>0.1285087530406699</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42">
+        <v>124</v>
+      </c>
+      <c r="C42">
+        <v>-0.001843891212568493</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0.0309216972859208</v>
+      </c>
+      <c r="F42">
+        <v>-0.1180550669313547</v>
+      </c>
+      <c r="G42">
+        <v>0.1328140243405103</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43">
+        <v>123</v>
+      </c>
+      <c r="C43">
+        <v>0.003172771307932802</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0.06726105729981163</v>
+      </c>
+      <c r="F43">
+        <v>-0.3208597111980185</v>
+      </c>
+      <c r="G43">
+        <v>0.2647180790344293</v>
       </c>
     </row>
   </sheetData>
